--- a/tiflow/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T12:23:45+00:00</t>
+    <t>2026-05-21T13:00:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T13:00:14+00:00</t>
+    <t>2026-05-21T14:08:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T14:08:29+00:00</t>
+    <t>2026-05-22T05:18:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T05:18:47+00:00</t>
+    <t>2026-05-22T10:01:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
